--- a/www/download/IND.gross_output.s.mv.zdW16.xlsx
+++ b/www/download/IND.gross_output.s.mv.zdW16.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>21610.99</t>
+          <t>18326219528.9142</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20797.768</t>
+          <t>17753128937.7122</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>21990.447</t>
+          <t>18641668864.7746</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>23645.123</t>
+          <t>19927589229.177</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>25064.774</t>
+          <t>20856922799.6132</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>26052.099</t>
+          <t>21356429110.2241</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>26768.507</t>
+          <t>21929331422.7996</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>28572.485</t>
+          <t>23380087307.9387</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>28808.141</t>
+          <t>23413929280.9966</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>29000.507</t>
+          <t>23501164643.9457</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>30078.4</t>
+          <t>24323154290.2927</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>34460.538</t>
+          <t>27538905587.7985</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>34146.365</t>
+          <t>27157590579.6992</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34223.998</t>
+          <t>27314385598.2693</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>26792.799</t>
+          <t>26792798983.3068</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8979.97</t>
+          <t>7197642659.91335</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8932.45</t>
+          <t>7151589232.35941</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8588.069</t>
+          <t>6848032648.39083</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>9029.471</t>
+          <t>7127425462.21803</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9141.716</t>
+          <t>7232693165.3338</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>8889.778</t>
+          <t>7040498538.50927</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9303.272</t>
+          <t>7356446214.07595</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>9441.473</t>
+          <t>7512835072.31264</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>9743.645</t>
+          <t>7720422810.11692</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9416.018</t>
+          <t>7336712674.48228</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>9746.873</t>
+          <t>7677221828.46287</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10752.139</t>
+          <t>8476624065.91225</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10728.875</t>
+          <t>8475572956.39846</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>11134.355</t>
+          <t>8836487937.85284</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>8259.388</t>
+          <t>8259388356.87435</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>11258.782</t>
+          <t>9236587537.27817</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10842.564</t>
+          <t>8908027640.06044</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10591.321</t>
+          <t>8684240796.7507</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>11327.443</t>
+          <t>9243698077.57196</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>12172.604</t>
+          <t>9900790775.06646</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>11855.878</t>
+          <t>9565632438.65398</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>12870.871</t>
+          <t>10421244147.6864</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>13620.119</t>
+          <t>11096570673.0336</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>14097.997</t>
+          <t>11434523174.4589</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>13041.867</t>
+          <t>10528305994.9496</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>14572.746</t>
+          <t>11912810005.1682</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>17041.179</t>
+          <t>13978720457.8264</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>15664.244</t>
+          <t>12821728444.4877</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>15507.761</t>
+          <t>12719636518.1426</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>13889.969</t>
+          <t>13889969244.0632</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6876.819</t>
+          <t>6056075406.78583</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6808.014</t>
+          <t>6014794219.04564</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6776.129</t>
+          <t>5999681047.73044</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6769.24</t>
+          <t>5989425316.20696</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6929.893</t>
+          <t>6206350464.43204</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6833.004</t>
+          <t>6071792843.75418</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7253.318</t>
+          <t>6428004439.96085</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>7444.939</t>
+          <t>6642742072.20247</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>7769.894</t>
+          <t>6919063216.48206</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7307.742</t>
+          <t>6377023120.82877</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>6454.612</t>
+          <t>5669959521.62501</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>6527.76</t>
+          <t>5720431417.75368</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6285.33</t>
+          <t>5478779709.00567</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6324.419</t>
+          <t>5507669312.54567</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5898.155</t>
+          <t>5898154580.46831</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>160614.011</t>
+          <t>144895736826.753</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>156906.105</t>
+          <t>140712925638.407</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>163445.867</t>
+          <t>145845374162.527</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>169352.866</t>
+          <t>150176604624.97</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>176542.243</t>
+          <t>157488013465.018</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>181427.556</t>
+          <t>161177759159.053</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>178225.115</t>
+          <t>158940962292.051</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>179518.727</t>
+          <t>160718024088.636</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>187531.82</t>
+          <t>166646620260.008</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>179676.585</t>
+          <t>158051172269.521</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>184778.199</t>
+          <t>162838034873.002</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>186320.706</t>
+          <t>164202509249.778</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>184855.52</t>
+          <t>162030849639.782</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>187364.254</t>
+          <t>164479979162.365</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>165354.943</t>
+          <t>165354943293.498</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>27957.486</t>
+          <t>24847537255.3067</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>27205.487</t>
+          <t>24271789451.0108</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>27313.251</t>
+          <t>24303821076.8178</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>28624.388</t>
+          <t>25436897347.7618</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30184.244</t>
+          <t>26694519584.836</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>30484.468</t>
+          <t>26600976977.3226</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>31297.423</t>
+          <t>27150482354.3965</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>30675.264</t>
+          <t>26595675259.5192</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30889.909</t>
+          <t>26687713698.2178</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>29448.211</t>
+          <t>25175094364.4227</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>31516.052</t>
+          <t>27070197887.1685</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>34196.706</t>
+          <t>29201232217.6822</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>35025.258</t>
+          <t>29782261645.0513</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>33537.742</t>
+          <t>28544072643.7855</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>29142.107</t>
+          <t>29142106509.1065</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2071059.115</t>
+          <t>1863347131814.51</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2027749.379</t>
+          <t>1839258523647.5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2027948.036</t>
+          <t>1847594287195.14</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2075980.695</t>
+          <t>1894288740499.86</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2151509.272</t>
+          <t>1963933658212.81</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2256495.604</t>
+          <t>2047704116761.31</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2428086.633</t>
+          <t>2208680433085.51</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2527290.885</t>
+          <t>2311860590197.13</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2685750.325</t>
+          <t>2430776377973.76</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2852439.68</t>
+          <t>2552047439680.91</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2809953.338</t>
+          <t>2532383352978.52</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>3122025.905</t>
+          <t>2795077497272.42</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3236448.452</t>
+          <t>2867741555476.54</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>3283111.799</t>
+          <t>2898221651989.22</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2842915.641</t>
+          <t>2842915641139.4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>557.219</t>
+          <t>477212468.834669</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>646.947</t>
+          <t>563020708.117875</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>729.198</t>
+          <t>626491950.751071</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>765.563</t>
+          <t>669265610.687618</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>688.884</t>
+          <t>604375114.314662</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>674.669</t>
+          <t>591565994.275607</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>623.622</t>
+          <t>540127989.446919</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>662.343</t>
+          <t>570745691.628135</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>794.808</t>
+          <t>681825647.683138</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>695.143</t>
+          <t>584012464.927286</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>632.873</t>
+          <t>534233705.51631</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>617.869</t>
+          <t>522466799.881098</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>558.049</t>
+          <t>470133491.719068</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>531.535</t>
+          <t>449081644.168673</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>437.662</t>
+          <t>437662154.168157</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11257.758</t>
+          <t>9652796690.96939</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>11015.456</t>
+          <t>9344095361.26279</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11229.144</t>
+          <t>9378703468.51897</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11340.269</t>
+          <t>9469858518.36153</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>11538.251</t>
+          <t>9752203742.25813</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11759.565</t>
+          <t>9944743968.47545</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>12191.006</t>
+          <t>10287997707.4335</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>12607.212</t>
+          <t>10632696364.7064</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>12903.225</t>
+          <t>10693970545.7108</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>11690.224</t>
+          <t>9523384543.3126</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>12088.646</t>
+          <t>9905618070.66193</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>13152.564</t>
+          <t>10674426476.8044</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>12328.74</t>
+          <t>10067004079.3767</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>12595.95</t>
+          <t>10320064940.8962</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>10366.443</t>
+          <t>10366442861.7273</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>78178.645</t>
+          <t>64242032276.6378</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>74981.878</t>
+          <t>61439444073.7433</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>72665.697</t>
+          <t>59100938673.3654</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>76973.109</t>
+          <t>61742519629.4127</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>78675.209</t>
+          <t>62963004569.6934</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>78710.999</t>
+          <t>62664041829.6961</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>83553.979</t>
+          <t>66482677979.3315</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>85665.267</t>
+          <t>68989911964.4131</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>86164.424</t>
+          <t>68709306466.1903</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>77612.887</t>
+          <t>61572500523.4215</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>80052.037</t>
+          <t>64800215364.6215</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>87533.564</t>
+          <t>71090555420.6706</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>82967.802</t>
+          <t>67514343383.9202</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>83806.494</t>
+          <t>68224280389.7992</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>67181.715</t>
+          <t>67181714981.7987</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6570.85</t>
+          <t>5428728137.41533</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6690.194</t>
+          <t>5544039656.65958</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6745.562</t>
+          <t>5599096383.1228</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7398.797</t>
+          <t>6053212394.24046</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7607.343</t>
+          <t>6173997824.90101</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7739.993</t>
+          <t>6246830476.14801</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7290.121</t>
+          <t>5780144966.1521</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7614.709</t>
+          <t>6191767370.78085</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>8104.414</t>
+          <t>6462955494.61979</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>7110.884</t>
+          <t>5658193409.94236</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>6530.37</t>
+          <t>5182314605.21346</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>6829.501</t>
+          <t>5398573772.78762</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>6715.798</t>
+          <t>5352424163.58861</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>7084.672</t>
+          <t>5718452019.74243</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>5475.95</t>
+          <t>5475949721.87987</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>38322.13</t>
+          <t>33926671211.7206</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>38932.853</t>
+          <t>34539068355.7007</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41500.234</t>
+          <t>36879211944.2269</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42834.185</t>
+          <t>37832921357.1439</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44894.016</t>
+          <t>39463786336.5105</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>46821.43</t>
+          <t>40971066528.1784</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>49580.943</t>
+          <t>43262425372.8833</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>50562.082</t>
+          <t>44095178249.2893</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>50302.038</t>
+          <t>43462913041.1208</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>41836.951</t>
+          <t>35841163032.347</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>44698.752</t>
+          <t>37720074285.5751</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>47445.792</t>
+          <t>39898703308.4221</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>44980.368</t>
+          <t>37635055108.2915</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>43392.507</t>
+          <t>36188281205.587</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>36698.684</t>
+          <t>36698683873.519</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1288.663</t>
+          <t>1187477960.33929</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1289.543</t>
+          <t>1175237689.28588</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1400.325</t>
+          <t>1271757760.68488</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1507.658</t>
+          <t>1357241522.10637</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1482.128</t>
+          <t>1345590413.79625</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1487.14</t>
+          <t>1350824162.22343</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1671.939</t>
+          <t>1506278678.46318</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1636.016</t>
+          <t>1474548156.35829</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1613.994</t>
+          <t>1442993819.20048</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1249.822</t>
+          <t>1106464169.30229</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1236.458</t>
+          <t>1096803867.36696</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1507.63</t>
+          <t>1329624310.61134</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1453.256</t>
+          <t>1272265504.82813</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1423.515</t>
+          <t>1232817254.56375</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1291.812</t>
+          <t>1291812427.38635</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6786.705</t>
+          <t>5762644646.22079</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6595.712</t>
+          <t>5540403688.75388</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6638.788</t>
+          <t>5606147375.78986</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7146.042</t>
+          <t>5949751766.44179</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7374.652</t>
+          <t>6153055258.29222</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7593.568</t>
+          <t>6248559317.44989</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7872.528</t>
+          <t>6443392807.05162</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7952.548</t>
+          <t>6535574393.55074</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>8588.333</t>
+          <t>7063104492.62541</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6449.92</t>
+          <t>5289403616.54527</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6385.312</t>
+          <t>5392899750.77175</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>6711.782</t>
+          <t>5661537083.93672</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>6572.398</t>
+          <t>5475768827.53104</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6338.944</t>
+          <t>5316098838.01644</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>5155.883</t>
+          <t>5155882581.45369</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>46483.444</t>
+          <t>40692318187.946</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>45661.444</t>
+          <t>39983625514.5616</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>44757.307</t>
+          <t>39058136626.1656</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>46825.718</t>
+          <t>40356710064.3275</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>50016.414</t>
+          <t>43216776423.7331</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>50211.829</t>
+          <t>43219756923.0075</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>51228.355</t>
+          <t>44078033032.9829</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>52340.881</t>
+          <t>45079525829.9178</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>53256.369</t>
+          <t>45648611172.0801</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>50438.75</t>
+          <t>43346318373.7467</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>49250.502</t>
+          <t>42557660814.3358</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>54656.043</t>
+          <t>47097467177.4333</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>51138.873</t>
+          <t>43975910718.2932</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>49086.517</t>
+          <t>42234759014.4047</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>41739.84</t>
+          <t>41739839739.0602</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>46451.482</t>
+          <t>39866009120.1593</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>46184.029</t>
+          <t>39699539196.3381</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>46390.289</t>
+          <t>39907141112.5945</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>47256.045</t>
+          <t>40678071322.8679</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>48136.853</t>
+          <t>41266575902.203</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>49116.754</t>
+          <t>41861886305.1773</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>49701.477</t>
+          <t>42635055147.3843</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>48611.915</t>
+          <t>41710639943.4709</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>46587.308</t>
+          <t>39770335211.8969</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>46824.306</t>
+          <t>39849559590.0174</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>47453.278</t>
+          <t>40319081134.0561</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>50438.265</t>
+          <t>42589119501.2956</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>51937.711</t>
+          <t>43843688824.4419</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>53714.401</t>
+          <t>45267810229.233</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>43269.247</t>
+          <t>43269247320.6309</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8318.716</t>
+          <t>7569412675.86768</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8152.208</t>
+          <t>7346575165.00383</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>7925.622</t>
+          <t>7133473194.30086</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8148.436</t>
+          <t>7376974660.90064</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>7899.596</t>
+          <t>7193493711.79536</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>8574.16</t>
+          <t>7792297810.5466</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8841.652</t>
+          <t>8012511775.58437</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>9100.526</t>
+          <t>8221875896.29856</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>8780.883</t>
+          <t>7889909219.09936</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>8473.293</t>
+          <t>7620430577.53412</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>7691.174</t>
+          <t>6802302111.96299</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>7468.977</t>
+          <t>6554771315.3505</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>6654.112</t>
+          <t>5849839741.75461</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>6825.378</t>
+          <t>5981443898.50655</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6325.235</t>
+          <t>6325234750.81282</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10852.418</t>
+          <t>9177206100.78468</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10725.497</t>
+          <t>9019600118.49311</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>10810.678</t>
+          <t>9130830948.86112</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>10631.393</t>
+          <t>8925997067.2627</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>10463.944</t>
+          <t>8818515389.78486</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10381.258</t>
+          <t>8767631919.49591</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>10501.07</t>
+          <t>8889774667.90282</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>10279.994</t>
+          <t>8595733032.50672</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>10010.646</t>
+          <t>8304412512.94135</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>9324.705</t>
+          <t>7670275070.16323</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>8706.525</t>
+          <t>7200882504.7976</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>8916.442</t>
+          <t>7412542416.14146</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>8218.747</t>
+          <t>6825516864.21968</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>8176.603</t>
+          <t>6766415734.43502</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>7450.546</t>
+          <t>7450546135.71559</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>162120.298</t>
+          <t>154506849002.011</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>170025.762</t>
+          <t>162847889410.49</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>182921.881</t>
+          <t>174517141301.308</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>200682.613</t>
+          <t>190625498858.968</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>199587.141</t>
+          <t>188997826013.943</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>178754.606</t>
+          <t>169561308639.701</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>176796.6</t>
+          <t>161734159037.641</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>183240.95</t>
+          <t>167156490803.53</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>187707.083</t>
+          <t>170591860787.375</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>196664.375</t>
+          <t>178040844736.124</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>200049.932</t>
+          <t>181807822667.705</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>201148.805</t>
+          <t>182422928808.317</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>218269.753</t>
+          <t>198015539825.246</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>238073.602</t>
+          <t>217778864291.945</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>241187.754</t>
+          <t>241187753875.776</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1249024.231</t>
+          <t>1161523881875.92</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1279284.897</t>
+          <t>1193268967845.55</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1319770.406</t>
+          <t>1236423340057.57</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1396292.597</t>
+          <t>1304949981034.73</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>1435081.517</t>
+          <t>1346618294856.36</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1420297.732</t>
+          <t>1336297857442.95</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>1410996.457</t>
+          <t>1328622117333.09</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1413235.59</t>
+          <t>1323079997077.16</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>1400121.588</t>
+          <t>1310348795910.59</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>1415091.274</t>
+          <t>1316024453442.07</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1429135.544</t>
+          <t>1329283859063.01</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1449690.345</t>
+          <t>1345681449875.16</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1615118.585</t>
+          <t>1486477257617.2</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1769913.439</t>
+          <t>1630788870922.18</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1737602.577</t>
+          <t>1737602577361.21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4025.151</t>
+          <t>3618428353.32083</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4599.33</t>
+          <t>4121848865.18492</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4583.766</t>
+          <t>4083289462.27368</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5076.083</t>
+          <t>4477215098.10321</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5290.409</t>
+          <t>4679076156.12117</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>5820.437</t>
+          <t>5124164403.17322</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6348.538</t>
+          <t>5576343495.57051</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>6049.528</t>
+          <t>5342790007.37113</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>5591.839</t>
+          <t>4918753920.02572</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>5205.993</t>
+          <t>4357488578.78025</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>3838.202</t>
+          <t>3217336175.05767</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>4488.818</t>
+          <t>3671831973.16641</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>4346.297</t>
+          <t>3578084370.48385</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>4811.275</t>
+          <t>3983264213.7407</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>4008.285</t>
+          <t>4008284760.40187</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>57386.568</t>
+          <t>49471606893.7185</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>57046.776</t>
+          <t>49264977630.2827</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>56706.19</t>
+          <t>48776355510.0501</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>58474.886</t>
+          <t>49877382054.1684</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>61120.938</t>
+          <t>52024855510.9556</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>60788.936</t>
+          <t>51512593943.3203</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>64928.591</t>
+          <t>54886382128.6259</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>64661.419</t>
+          <t>54906247652.8277</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>65194.909</t>
+          <t>54845915981.1623</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>56578.123</t>
+          <t>46988556276.37</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>60811.676</t>
+          <t>50295268154.5197</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>65923.151</t>
+          <t>54429293711.6319</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>59194.135</t>
+          <t>48804439681.9936</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>56853.877</t>
+          <t>46799721522.5676</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>46472.035</t>
+          <t>46472035062.9756</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>199434.221</t>
+          <t>158781102527.257</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>189782.347</t>
+          <t>149260433837.411</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>182298.076</t>
+          <t>141874667057.614</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>188773.688</t>
+          <t>146329445471.26</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>196162.802</t>
+          <t>152841794750.58</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>195320.756</t>
+          <t>152084928057.435</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>198845.132</t>
+          <t>156671355282.309</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>193192.315</t>
+          <t>153570695955.9</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>199806.412</t>
+          <t>156874972563.273</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>177338.015</t>
+          <t>131768586899.708</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>184190.677</t>
+          <t>137514254175.907</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>204612.514</t>
+          <t>151788838633.266</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>203104.568</t>
+          <t>150744892295.737</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>191019.567</t>
+          <t>145639661548.609</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>144683.9</t>
+          <t>144683899701.799</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>74286.722</t>
+          <t>62576462946.8099</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>71976.085</t>
+          <t>60536788907.5697</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>74334.171</t>
+          <t>62239352649.597</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>77529.433</t>
+          <t>64881793324.501</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>84144.958</t>
+          <t>69959637636.5039</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>83662.509</t>
+          <t>68234761060.8344</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>89863.821</t>
+          <t>73939110046.5509</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>86749.974</t>
+          <t>71846510002.1379</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>90924.344</t>
+          <t>75152282570.1225</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>87386.635</t>
+          <t>72068609227.8582</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>90763.059</t>
+          <t>74926167937.8142</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>105945.19</t>
+          <t>86182880962.3513</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>105853.328</t>
+          <t>85695211700.2678</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>109006.422</t>
+          <t>88752268867.0716</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>89188.755</t>
+          <t>89188754770.9213</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3239.897</t>
+          <t>2850424481.34571</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3124.066</t>
+          <t>2790570996.66151</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3163.735</t>
+          <t>2829121997.86594</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3265.421</t>
+          <t>2928884921.38315</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3058.904</t>
+          <t>2758641647.65947</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3143.944</t>
+          <t>2823488880.74509</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3157.531</t>
+          <t>2831136064.64511</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3037.33</t>
+          <t>2745034740.61769</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3163.674</t>
+          <t>2845422413.78938</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2613.786</t>
+          <t>2284538387.09381</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2456.067</t>
+          <t>2168725763.82076</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2612.015</t>
+          <t>2311517178.33692</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2630.328</t>
+          <t>2322196796.35386</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2618.17</t>
+          <t>2304569732.99074</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2645.597</t>
+          <t>2645597486.84344</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>428.739</t>
+          <t>356442520.658564</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>448.488</t>
+          <t>376396496.174488</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>440.588</t>
+          <t>374082862.323363</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>477.912</t>
+          <t>396889018.981221</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>519.177</t>
+          <t>414012625.966038</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>521.483</t>
+          <t>405580318.206457</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>559.275</t>
+          <t>444803219.733393</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>583.017</t>
+          <t>460633925.116932</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>659.208</t>
+          <t>528655829.683661</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>635.932</t>
+          <t>506820762.45083</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>706.406</t>
+          <t>576487909.033099</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>690.143</t>
+          <t>551805777.929653</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>683.93</t>
+          <t>545279899.945582</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>622.339</t>
+          <t>475676404.210519</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>494.687</t>
+          <t>494687022.384447</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2149.848</t>
+          <t>1841406992.94523</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2199.587</t>
+          <t>1936923789.13775</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2187.453</t>
+          <t>1957990425.94009</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2297.286</t>
+          <t>2055356652.11087</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2211.875</t>
+          <t>1985675187.85459</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2235.748</t>
+          <t>1992562513.75745</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2466.482</t>
+          <t>2190263016.94049</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2446.104</t>
+          <t>2137406764.1883</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2434.457</t>
+          <t>2125181390.6093</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1872.696</t>
+          <t>1600803743.1539</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1707.733</t>
+          <t>1461411689.41951</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1883.878</t>
+          <t>1596034056.94888</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1974.695</t>
+          <t>1665890147.92452</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1935.881</t>
+          <t>1647396701.20507</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1704.145</t>
+          <t>1704145258.79232</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>76063.501</t>
+          <t>69693746831.7497</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>74978.157</t>
+          <t>68326328345.0979</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>74644.033</t>
+          <t>67768909413.1932</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>75030.433</t>
+          <t>68453445158.5328</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>77985.678</t>
+          <t>71561964133.3476</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>77965.015</t>
+          <t>71489743842.6525</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>81550.897</t>
+          <t>74799000757.8533</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>82531.618</t>
+          <t>75908236162.6948</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>82522.877</t>
+          <t>75759047140.2054</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>78665.003</t>
+          <t>72037324467.9419</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>81012.14</t>
+          <t>74402496584.4899</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>82200.415</t>
+          <t>75324892514.0301</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>84224.075</t>
+          <t>77441712046.0832</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>84195.039</t>
+          <t>77381249441.4538</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>77703.194</t>
+          <t>77703193653.9907</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>344.393</t>
+          <t>306585220.625564</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>313.032</t>
+          <t>278883768.473924</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>297.283</t>
+          <t>267736149.361996</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>324.475</t>
+          <t>286986152.069177</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>302.741</t>
+          <t>268412079.634193</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>302.461</t>
+          <t>268561673.286777</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>307.826</t>
+          <t>268786231.243782</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>325.752</t>
+          <t>285426441.001786</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>387.901</t>
+          <t>339047729.548312</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>350.609</t>
+          <t>298413679.431971</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>363.03</t>
+          <t>313087086.470156</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>329.691</t>
+          <t>280097988.509356</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>344.425</t>
+          <t>293380635.548263</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>333.612</t>
+          <t>283675339.275305</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>258.773</t>
+          <t>258773483.442973</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>19040.825</t>
+          <t>16250773514.7872</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>19985.371</t>
+          <t>17329269916.9047</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>20773.454</t>
+          <t>17871729712.3347</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>25244.764</t>
+          <t>21718323838.5912</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>23990.593</t>
+          <t>20567527379.5371</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>23442.3</t>
+          <t>20000565793.4604</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>23777.881</t>
+          <t>20239726725.1361</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>24589.287</t>
+          <t>20902774126.5372</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>26748.361</t>
+          <t>22646348969.9851</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>28822.326</t>
+          <t>23785714483.9376</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>29804.992</t>
+          <t>24442707482.3807</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>31729.883</t>
+          <t>25978076137.4933</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>29834.984</t>
+          <t>24513125820.2556</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>33929.876</t>
+          <t>27121034349.4027</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>27558.282</t>
+          <t>27558281805.3374</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>33750.295</t>
+          <t>31691776893.8988</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>34594.954</t>
+          <t>32705699380.721</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>31648.578</t>
+          <t>29827053693.3468</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>31666.728</t>
+          <t>29810669741.5357</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>32421.205</t>
+          <t>30532936176.2958</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>33160.93</t>
+          <t>31132099014.3713</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>34281.138</t>
+          <t>32079719189.8819</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>35807.874</t>
+          <t>33436401743.7265</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>37669.205</t>
+          <t>35007771840.3784</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>36455.098</t>
+          <t>33939587916.9671</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>37474.727</t>
+          <t>34692807326.8768</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>39193.447</t>
+          <t>36127022776.3459</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>37940.84</t>
+          <t>35008942531.4313</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>37971.611</t>
+          <t>34961182816.6307</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>35138.425</t>
+          <t>35138424815.4553</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>14026.61</t>
+          <t>12680045252.954</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13831.187</t>
+          <t>12535434086.3387</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>13516.389</t>
+          <t>12221670546.1304</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>13404.107</t>
+          <t>12062810220.6729</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>13832.174</t>
+          <t>12441198068.5348</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>13074.048</t>
+          <t>11722742375.8453</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>13124.006</t>
+          <t>11663695820.7522</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>13210.415</t>
+          <t>11721112317.5624</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>13418.515</t>
+          <t>11786463544.5444</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>11542.177</t>
+          <t>10086534840.6854</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>11403.49</t>
+          <t>9970525975.96004</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12027.679</t>
+          <t>10447106944.5326</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11144.634</t>
+          <t>9591734525.50566</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>11211.214</t>
+          <t>9708865456.96416</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>9877.416</t>
+          <t>9877415532.93961</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>33634.822</t>
+          <t>29210998340.8183</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>32784.755</t>
+          <t>28486845306.4439</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>27376.326</t>
+          <t>23841654046.3862</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27904.437</t>
+          <t>24446707434.012</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>26403.587</t>
+          <t>23448158113.6495</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>26141.405</t>
+          <t>23212369682.4401</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>25240.109</t>
+          <t>22561676152.278</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>25830.541</t>
+          <t>23090461816.6291</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>25287.108</t>
+          <t>22499052601.3867</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>24528.653</t>
+          <t>21696179391.8423</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>23154.66</t>
+          <t>20826146843.9225</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>23500.08</t>
+          <t>21008368338.0278</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>18121.984</t>
+          <t>15986360152.1483</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>18063.239</t>
+          <t>15909839937.5892</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>16027.668</t>
+          <t>16027668110.1342</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>158393.773</t>
+          <t>143803626418.53</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>158486.666</t>
+          <t>144113340729.802</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>155881.96</t>
+          <t>140389431712.969</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>158003.526</t>
+          <t>141081759894.244</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>151889.552</t>
+          <t>140521347463.444</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>155065.262</t>
+          <t>139573013467.587</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>153985.616</t>
+          <t>138780712392.905</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>154148.048</t>
+          <t>141246483209.448</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>144935.907</t>
+          <t>131252648684.358</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>138909.145</t>
+          <t>125711006643.574</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>140394.951</t>
+          <t>126327518849.704</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>140108.613</t>
+          <t>124947696988.778</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>143654.52</t>
+          <t>127646839154.717</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>138107.476</t>
+          <t>121846558536.601</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>113940.584</t>
+          <t>113940584141.081</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4608.211</t>
+          <t>3895616743.44967</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4604.776</t>
+          <t>3861400451.33319</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4549.374</t>
+          <t>3796235792.55269</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4631.658</t>
+          <t>3872944000.46614</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4709.672</t>
+          <t>3957020805.06821</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4812.199</t>
+          <t>3991444651.98832</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>5274.019</t>
+          <t>4387753277.1857</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>5578.699</t>
+          <t>4666746294.04871</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5707.804</t>
+          <t>4742464852.15569</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5659.673</t>
+          <t>4659359568.83589</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>5350.436</t>
+          <t>4391405598.93291</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>5917.614</t>
+          <t>4760540806.45639</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>5752.929</t>
+          <t>4714661372.05332</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>5847.994</t>
+          <t>4800109777.80764</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>4899.932</t>
+          <t>4899931645.25881</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2065.576</t>
+          <t>1820122840.80356</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2063.32</t>
+          <t>1818034117.86821</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2067.554</t>
+          <t>1829655283.88765</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2127.72</t>
+          <t>1882856719.01915</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2322.279</t>
+          <t>2035677526.26455</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2274.758</t>
+          <t>1989646943.23468</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2324.454</t>
+          <t>2029475161.2875</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2357.134</t>
+          <t>2065231031.10271</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2397.226</t>
+          <t>2088436377.00394</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2171.944</t>
+          <t>1881664818.9053</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2163.341</t>
+          <t>1886537125.12623</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2249.367</t>
+          <t>1943180651.84343</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2087.254</t>
+          <t>1800784027.89444</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2020.276</t>
+          <t>1732317774.5086</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1767.7</t>
+          <t>1767700261.19881</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9731.542</t>
+          <t>8146413855.63023</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>9199.535</t>
+          <t>7703714104.50408</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>9040.398</t>
+          <t>7538978611.5376</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>9358.92</t>
+          <t>7704689452.92551</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>9974.81</t>
+          <t>8185163366.66737</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>10125.868</t>
+          <t>8271082588.37756</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>10208.558</t>
+          <t>8285021456.79083</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>10259.024</t>
+          <t>8379042946.8786</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>10438.949</t>
+          <t>8448277981.26453</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>9289.064</t>
+          <t>7538292031.82342</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>9576.947</t>
+          <t>7871744797.62031</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10331.371</t>
+          <t>8443124307.34255</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>9914.805</t>
+          <t>8078731838.39138</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>9929.628</t>
+          <t>8069820990.38977</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>8026.465</t>
+          <t>8026465010.00051</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>66861.202</t>
+          <t>58665153130.6895</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>63617.06</t>
+          <t>56558187039.7788</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>59901.262</t>
+          <t>53467681131.3394</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>60758.672</t>
+          <t>54093924947.5943</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>63665.363</t>
+          <t>56299565088.2715</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>63541.612</t>
+          <t>55377981324.4553</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>62525.036</t>
+          <t>53868676937.166</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>61665.672</t>
+          <t>52988121265.2738</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>61703.958</t>
+          <t>51948633489.3483</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>58349.147</t>
+          <t>48071347740.5294</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>64166.555</t>
+          <t>54136007772.7666</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>68936.069</t>
+          <t>58221957750.9745</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>70302.258</t>
+          <t>59568918251.5574</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>74866.841</t>
+          <t>63540960204.7121</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>70110.755</t>
+          <t>70110755090.1184</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>50310.319</t>
+          <t>43493951502.9625</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>45542.621</t>
+          <t>38979197809.7149</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>48126.025</t>
+          <t>40969354838.7649</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>51167.487</t>
+          <t>43482041368.9089</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>56382.533</t>
+          <t>47803436727.6776</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>56243.163</t>
+          <t>47029762660.7121</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>58235.921</t>
+          <t>48553896283.0045</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>57594.04</t>
+          <t>48597904780.0074</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>57245.782</t>
+          <t>47911811999.766</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>50293.077</t>
+          <t>41813361075.0403</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>56740.112</t>
+          <t>47843650530.2676</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>60078.166</t>
+          <t>50058323869.3525</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>59053.763</t>
+          <t>48772816719.9938</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>59248.559</t>
+          <t>49057862823.9945</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>51222.588</t>
+          <t>51222587648.5545</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>279819.374</t>
+          <t>236343039397.868</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>263033.544</t>
+          <t>221130435504.106</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>261346.943</t>
+          <t>218729419087.842</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>263265.32</t>
+          <t>220590295633.016</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>274623.781</t>
+          <t>229464213930.877</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>287294.928</t>
+          <t>237789903464.14</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>292910.514</t>
+          <t>241527998662.097</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>279152.76</t>
+          <t>229169505089.862</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>276124.958</t>
+          <t>225043369249.361</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>232119.324</t>
+          <t>188367314993.018</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>238036.544</t>
+          <t>191579887546.213</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>259656.313</t>
+          <t>208573217449.159</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>261581.919</t>
+          <t>210869522806.899</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>256878.437</t>
+          <t>211295199862.33</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>217618.112</t>
+          <t>217618111854.757</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2575755.568</t>
+          <t>2300768937047.84</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2624857.49</t>
+          <t>2360181047280.94</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2794971.317</t>
+          <t>2494307609922.48</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2908591.885</t>
+          <t>2598124684814.83</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>3000494.641</t>
+          <t>2695136188499.57</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>3149706.911</t>
+          <t>2805045113717.23</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3292823.966</t>
+          <t>2931403314332.88</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>3305531.961</t>
+          <t>2981385858869.04</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>3401263.291</t>
+          <t>3065741114664.77</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>3501719.759</t>
+          <t>3162837882356.66</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>3496785.781</t>
+          <t>3162754464633.32</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>3667927.15</t>
+          <t>3314153375999.13</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>3936326.315</t>
+          <t>3566490825137.71</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>4121844.364</t>
+          <t>3773590774035.19</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>3935478.768</t>
+          <t>3935478768125.06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7658947.361</t>
+          <t>6860039946171.88</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7654874.728</t>
+          <t>6892083300043.79</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7866338.425</t>
+          <t>7072872405870.13</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>8168590.894</t>
+          <t>7342391228669.68</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8425170.968</t>
+          <t>7597567277813.04</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>8667951.658</t>
+          <t>7770156748151.05</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>9007104.07</t>
+          <t>8072723326559.19</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>9115315.465</t>
+          <t>8221862054094.95</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>9373798.993</t>
+          <t>8414486407560.39</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>9523696.172</t>
+          <t>8513451410812.62</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>9540839.098</t>
+          <t>8551719873143.54</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>10158770.256</t>
+          <t>9068534099411.33</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>10698797.383</t>
+          <t>9527412301385.28</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>11094375.661</t>
+          <t>9928081317318.42</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>10172462.93</t>
+          <t>10172462929502.8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4337,84 +4342,84 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2986.708</t>
+          <t>2717704660.46223</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2927.801</t>
+          <t>2666937674.40891</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3036.426</t>
+          <t>2749285647.88613</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>3028.853</t>
+          <t>2737204738.09074</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>3204.879</t>
+          <t>2889741638.55864</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>3121.824</t>
+          <t>2805889460.6926</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>3193.371</t>
+          <t>2855240185.47796</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>3231.585</t>
+          <t>2897009426.46585</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>3387.849</t>
+          <t>3003443513.02517</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>3168.019</t>
+          <t>2787792840.1075</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>3049.486</t>
+          <t>2674452605.14853</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>3019.204</t>
+          <t>2635767514.7016</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>2854.184</t>
+          <t>2481902775.62649</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2801.254</t>
+          <t>2423836677.52324</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2406.802</t>
+          <t>2406801568.83427</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4424,84 +4429,84 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>11056.571</t>
+          <t>9198092515.02885</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10672.277</t>
+          <t>8885204829.14715</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>10526.886</t>
+          <t>8748009043.62626</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>10777.033</t>
+          <t>8997282499.94534</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>10517.03</t>
+          <t>8842401184.84076</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>10913.449</t>
+          <t>9113180700.07789</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>11370.433</t>
+          <t>9527247206.71712</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>11201.406</t>
+          <t>9452911178.99477</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>11643.453</t>
+          <t>9787338471.08483</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>11121.539</t>
+          <t>9179906503.67377</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>10785.911</t>
+          <t>8926595112.38423</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>12444.015</t>
+          <t>10260755509.9174</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>12373.467</t>
+          <t>10164183397.4483</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>12531.619</t>
+          <t>10402918318.5927</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>10372.485</t>
+          <t>10372484654.484</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4511,84 +4516,84 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4977.193</t>
+          <t>3937315903.43706</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4777.318</t>
+          <t>3853113625.72378</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4781.985</t>
+          <t>3863614681.44266</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4878.519</t>
+          <t>3919251149.50189</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>4950.69</t>
+          <t>4068188090.45955</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>5109.623</t>
+          <t>4129990466.87408</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>5146.068</t>
+          <t>4170392080.31901</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>5506.037</t>
+          <t>4518298903.14897</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>5614.162</t>
+          <t>4520307048.35747</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>5107.29</t>
+          <t>4040407285.70311</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>5090.553</t>
+          <t>4041686136.56444</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>5522.959</t>
+          <t>4308305035.1152</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>5429.506</t>
+          <t>4368778697.93788</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>5559.204</t>
+          <t>4461428439.40002</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>4421.228</t>
+          <t>4421228146.20493</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4600,7 +4605,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4612,7 +4617,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4624,7 +4629,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4636,7 +4641,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4648,7 +4653,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4695,6 +4700,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4729,6 +4739,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
